--- a/content-files/Physics.xlsx
+++ b/content-files/Physics.xlsx
@@ -582,7 +582,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>26/08/2026 16:13:50</t>
+          <t>27/08/2026 13:45:50</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -1490,7 +1490,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>A bullet is shot horizontally from shoulder height ($$1.5\,\text{m}$$) with an initial speed $$200\,\tfrac{\text{m}}{\text{s}}$$.</t>
+          <t>A bullet is shot horizontally from shoulder height $$(1.5\,\text{m})$$ with an initial speed $$200\,\tfrac{\text{m}}{\text{s}}$$.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
@@ -1529,7 +1529,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>26/08/2026 16:13:50</t>
+          <t>27/08/2026 13:45:50</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
